--- a/healthcare_assessment_forms/007_premature_retinopathy_assessment_form--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/007_premature_retinopathy_assessment_form--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'no_issue'}</t>
+          <t>no_issue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'No issue'}</t>
+          <t>No issue</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Mild'}</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'medication'}</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Medication'}</t>
+          <t>Medication</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'surgery'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Surgery'}</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'no_issue'}</t>
+          <t>no_issue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'No issue'}</t>
+          <t>No issue</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'possible_issue'}</t>
+          <t>possible_issue</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Possible issue'}</t>
+          <t>Possible issue</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'issue'}</t>
+          <t>issue</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Issue'}</t>
+          <t>Issue</t>
         </is>
       </c>
     </row>
